--- a/data/results/folder_ekup_Yemelyanovo_2023/ekup_Yemelyanovo_2023_fires_profiling_report.xlsx
+++ b/data/results/folder_ekup_Yemelyanovo_2023/ekup_Yemelyanovo_2023_fires_profiling_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M274"/>
+  <dimension ref="A1:V274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,51 @@
           <t>drop_reasons</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>profiling_candidate_to_drop</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>mandatory_feature_detected</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>protected_feature_id</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>protected_feature_label</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>protection_scope</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>protection_rule</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>protection_match</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>protection_reason</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>protected_from_drop</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -529,6 +574,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -576,6 +636,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -623,6 +698,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -670,6 +760,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N5" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -717,6 +822,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N6" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -764,6 +884,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N7" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -811,6 +946,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N8" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -858,6 +1008,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N9" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -905,6 +1070,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N10" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -952,6 +1132,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N11" t="b">
+        <v>1</v>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -999,6 +1194,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N12" t="b">
+        <v>1</v>
+      </c>
+      <c r="O12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1046,6 +1256,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N13" t="b">
+        <v>1</v>
+      </c>
+      <c r="O13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1094,6 +1319,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N14" t="b">
+        <v>1</v>
+      </c>
+      <c r="O14" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1141,6 +1381,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N15" t="b">
+        <v>1</v>
+      </c>
+      <c r="O15" t="b">
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1188,6 +1443,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N16" t="b">
+        <v>1</v>
+      </c>
+      <c r="O16" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1235,6 +1505,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N17" t="b">
+        <v>1</v>
+      </c>
+      <c r="O17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1282,6 +1567,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N18" t="b">
+        <v>1</v>
+      </c>
+      <c r="O18" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1329,6 +1629,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N19" t="b">
+        <v>1</v>
+      </c>
+      <c r="O19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1376,6 +1691,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N20" t="b">
+        <v>1</v>
+      </c>
+      <c r="O20" t="b">
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1423,6 +1753,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N21" t="b">
+        <v>1</v>
+      </c>
+      <c r="O21" t="b">
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1470,6 +1815,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N22" t="b">
+        <v>1</v>
+      </c>
+      <c r="O22" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1517,6 +1877,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N23" t="b">
+        <v>1</v>
+      </c>
+      <c r="O23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1564,6 +1939,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N24" t="b">
+        <v>1</v>
+      </c>
+      <c r="O24" t="b">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1611,6 +2001,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N25" t="b">
+        <v>1</v>
+      </c>
+      <c r="O25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1658,6 +2063,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N26" t="b">
+        <v>1</v>
+      </c>
+      <c r="O26" t="b">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1705,6 +2125,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N27" t="b">
+        <v>1</v>
+      </c>
+      <c r="O27" t="b">
+        <v>0</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1752,6 +2187,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N28" t="b">
+        <v>1</v>
+      </c>
+      <c r="O28" t="b">
+        <v>0</v>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1799,6 +2249,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O29" t="b">
+        <v>0</v>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1846,6 +2311,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N30" t="b">
+        <v>1</v>
+      </c>
+      <c r="O30" t="b">
+        <v>0</v>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1893,6 +2373,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N31" t="b">
+        <v>1</v>
+      </c>
+      <c r="O31" t="b">
+        <v>0</v>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1940,6 +2435,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N32" t="b">
+        <v>1</v>
+      </c>
+      <c r="O32" t="b">
+        <v>0</v>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1987,6 +2497,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O33" t="b">
+        <v>0</v>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2034,6 +2559,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N34" t="b">
+        <v>1</v>
+      </c>
+      <c r="O34" t="b">
+        <v>0</v>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2081,6 +2621,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N35" t="b">
+        <v>1</v>
+      </c>
+      <c r="O35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2128,6 +2683,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N36" t="b">
+        <v>1</v>
+      </c>
+      <c r="O36" t="b">
+        <v>0</v>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2175,6 +2745,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N37" t="b">
+        <v>1</v>
+      </c>
+      <c r="O37" t="b">
+        <v>0</v>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2222,6 +2807,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N38" t="b">
+        <v>1</v>
+      </c>
+      <c r="O38" t="b">
+        <v>0</v>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2269,6 +2869,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N39" t="b">
+        <v>1</v>
+      </c>
+      <c r="O39" t="b">
+        <v>0</v>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2316,6 +2931,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N40" t="b">
+        <v>1</v>
+      </c>
+      <c r="O40" t="b">
+        <v>0</v>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2363,6 +2993,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N41" t="b">
+        <v>1</v>
+      </c>
+      <c r="O41" t="b">
+        <v>0</v>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2410,6 +3055,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N42" t="b">
+        <v>1</v>
+      </c>
+      <c r="O42" t="b">
+        <v>0</v>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2457,6 +3117,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N43" t="b">
+        <v>1</v>
+      </c>
+      <c r="O43" t="b">
+        <v>0</v>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2504,6 +3179,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N44" t="b">
+        <v>1</v>
+      </c>
+      <c r="O44" t="b">
+        <v>0</v>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2551,6 +3241,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N45" t="b">
+        <v>1</v>
+      </c>
+      <c r="O45" t="b">
+        <v>0</v>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2598,6 +3303,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N46" t="b">
+        <v>1</v>
+      </c>
+      <c r="O46" t="b">
+        <v>0</v>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2645,6 +3365,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N47" t="b">
+        <v>1</v>
+      </c>
+      <c r="O47" t="b">
+        <v>0</v>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2692,6 +3427,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N48" t="b">
+        <v>1</v>
+      </c>
+      <c r="O48" t="b">
+        <v>0</v>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2739,6 +3489,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N49" t="b">
+        <v>1</v>
+      </c>
+      <c r="O49" t="b">
+        <v>0</v>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2786,6 +3551,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N50" t="b">
+        <v>1</v>
+      </c>
+      <c r="O50" t="b">
+        <v>0</v>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2833,6 +3613,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти нет разброса', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N51" t="b">
+        <v>1</v>
+      </c>
+      <c r="O51" t="b">
+        <v>0</v>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2880,6 +3675,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N52" t="b">
+        <v>1</v>
+      </c>
+      <c r="O52" t="b">
+        <v>0</v>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2927,6 +3737,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N53" t="b">
+        <v>1</v>
+      </c>
+      <c r="O53" t="b">
+        <v>0</v>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2974,6 +3799,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N54" t="b">
+        <v>1</v>
+      </c>
+      <c r="O54" t="b">
+        <v>0</v>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3021,6 +3861,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N55" t="b">
+        <v>1</v>
+      </c>
+      <c r="O55" t="b">
+        <v>0</v>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3068,6 +3923,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N56" t="b">
+        <v>1</v>
+      </c>
+      <c r="O56" t="b">
+        <v>0</v>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3115,6 +3985,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N57" t="b">
+        <v>1</v>
+      </c>
+      <c r="O57" t="b">
+        <v>0</v>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3162,6 +4047,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N58" t="b">
+        <v>1</v>
+      </c>
+      <c r="O58" t="b">
+        <v>0</v>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3209,6 +4109,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N59" t="b">
+        <v>1</v>
+      </c>
+      <c r="O59" t="b">
+        <v>0</v>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3256,6 +4171,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N60" t="b">
+        <v>1</v>
+      </c>
+      <c r="O60" t="b">
+        <v>0</v>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3303,6 +4233,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N61" t="b">
+        <v>1</v>
+      </c>
+      <c r="O61" t="b">
+        <v>0</v>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3350,6 +4295,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N62" t="b">
+        <v>1</v>
+      </c>
+      <c r="O62" t="b">
+        <v>0</v>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3397,6 +4357,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N63" t="b">
+        <v>1</v>
+      </c>
+      <c r="O63" t="b">
+        <v>0</v>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3444,6 +4419,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N64" t="b">
+        <v>1</v>
+      </c>
+      <c r="O64" t="b">
+        <v>0</v>
+      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3491,6 +4481,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N65" t="b">
+        <v>1</v>
+      </c>
+      <c r="O65" t="b">
+        <v>0</v>
+      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3538,6 +4543,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N66" t="b">
+        <v>1</v>
+      </c>
+      <c r="O66" t="b">
+        <v>0</v>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3585,6 +4605,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N67" t="b">
+        <v>1</v>
+      </c>
+      <c r="O67" t="b">
+        <v>0</v>
+      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3632,6 +4667,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N68" t="b">
+        <v>1</v>
+      </c>
+      <c r="O68" t="b">
+        <v>0</v>
+      </c>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3679,6 +4729,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N69" t="b">
+        <v>1</v>
+      </c>
+      <c r="O69" t="b">
+        <v>0</v>
+      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3726,6 +4791,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N70" t="b">
+        <v>1</v>
+      </c>
+      <c r="O70" t="b">
+        <v>0</v>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3773,6 +4853,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N71" t="b">
+        <v>1</v>
+      </c>
+      <c r="O71" t="b">
+        <v>0</v>
+      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3820,6 +4915,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N72" t="b">
+        <v>1</v>
+      </c>
+      <c r="O72" t="b">
+        <v>0</v>
+      </c>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3867,6 +4977,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N73" t="b">
+        <v>1</v>
+      </c>
+      <c r="O73" t="b">
+        <v>0</v>
+      </c>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3914,6 +5039,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N74" t="b">
+        <v>1</v>
+      </c>
+      <c r="O74" t="b">
+        <v>0</v>
+      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3961,6 +5101,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N75" t="b">
+        <v>1</v>
+      </c>
+      <c r="O75" t="b">
+        <v>0</v>
+      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4008,6 +5163,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N76" t="b">
+        <v>1</v>
+      </c>
+      <c r="O76" t="b">
+        <v>0</v>
+      </c>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4055,6 +5225,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N77" t="b">
+        <v>1</v>
+      </c>
+      <c r="O77" t="b">
+        <v>0</v>
+      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4102,6 +5287,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N78" t="b">
+        <v>1</v>
+      </c>
+      <c r="O78" t="b">
+        <v>0</v>
+      </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4149,6 +5349,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N79" t="b">
+        <v>1</v>
+      </c>
+      <c r="O79" t="b">
+        <v>0</v>
+      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4196,6 +5411,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N80" t="b">
+        <v>1</v>
+      </c>
+      <c r="O80" t="b">
+        <v>0</v>
+      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4243,6 +5473,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N81" t="b">
+        <v>1</v>
+      </c>
+      <c r="O81" t="b">
+        <v>0</v>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4290,6 +5535,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N82" t="b">
+        <v>1</v>
+      </c>
+      <c r="O82" t="b">
+        <v>0</v>
+      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4337,6 +5597,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O83" t="b">
+        <v>0</v>
+      </c>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4384,6 +5659,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N84" t="b">
+        <v>1</v>
+      </c>
+      <c r="O84" t="b">
+        <v>0</v>
+      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4431,6 +5721,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N85" t="b">
+        <v>1</v>
+      </c>
+      <c r="O85" t="b">
+        <v>0</v>
+      </c>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4478,6 +5783,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N86" t="b">
+        <v>1</v>
+      </c>
+      <c r="O86" t="b">
+        <v>0</v>
+      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4525,6 +5845,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N87" t="b">
+        <v>1</v>
+      </c>
+      <c r="O87" t="b">
+        <v>0</v>
+      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4572,6 +5907,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N88" t="b">
+        <v>1</v>
+      </c>
+      <c r="O88" t="b">
+        <v>0</v>
+      </c>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4619,6 +5969,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N89" t="b">
+        <v>1</v>
+      </c>
+      <c r="O89" t="b">
+        <v>0</v>
+      </c>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4666,6 +6031,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N90" t="b">
+        <v>1</v>
+      </c>
+      <c r="O90" t="b">
+        <v>0</v>
+      </c>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4713,6 +6093,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N91" t="b">
+        <v>1</v>
+      </c>
+      <c r="O91" t="b">
+        <v>0</v>
+      </c>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4760,6 +6155,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N92" t="b">
+        <v>1</v>
+      </c>
+      <c r="O92" t="b">
+        <v>0</v>
+      </c>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4807,6 +6217,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N93" t="b">
+        <v>1</v>
+      </c>
+      <c r="O93" t="b">
+        <v>0</v>
+      </c>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4854,6 +6279,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N94" t="b">
+        <v>1</v>
+      </c>
+      <c r="O94" t="b">
+        <v>0</v>
+      </c>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4901,6 +6341,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N95" t="b">
+        <v>1</v>
+      </c>
+      <c r="O95" t="b">
+        <v>0</v>
+      </c>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4948,6 +6403,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N96" t="b">
+        <v>1</v>
+      </c>
+      <c r="O96" t="b">
+        <v>0</v>
+      </c>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4995,6 +6465,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N97" t="b">
+        <v>1</v>
+      </c>
+      <c r="O97" t="b">
+        <v>0</v>
+      </c>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5042,6 +6527,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N98" t="b">
+        <v>1</v>
+      </c>
+      <c r="O98" t="b">
+        <v>0</v>
+      </c>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5089,6 +6589,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N99" t="b">
+        <v>1</v>
+      </c>
+      <c r="O99" t="b">
+        <v>0</v>
+      </c>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5136,6 +6651,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N100" t="b">
+        <v>1</v>
+      </c>
+      <c r="O100" t="b">
+        <v>0</v>
+      </c>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5183,6 +6713,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N101" t="b">
+        <v>1</v>
+      </c>
+      <c r="O101" t="b">
+        <v>0</v>
+      </c>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr"/>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5230,6 +6775,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N102" t="b">
+        <v>1</v>
+      </c>
+      <c r="O102" t="b">
+        <v>0</v>
+      </c>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5277,6 +6837,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N103" t="b">
+        <v>1</v>
+      </c>
+      <c r="O103" t="b">
+        <v>0</v>
+      </c>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr"/>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5324,6 +6899,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N104" t="b">
+        <v>1</v>
+      </c>
+      <c r="O104" t="b">
+        <v>0</v>
+      </c>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr"/>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5371,6 +6961,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N105" t="b">
+        <v>1</v>
+      </c>
+      <c r="O105" t="b">
+        <v>0</v>
+      </c>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5418,6 +7023,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N106" t="b">
+        <v>1</v>
+      </c>
+      <c r="O106" t="b">
+        <v>0</v>
+      </c>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="inlineStr"/>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5465,6 +7085,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N107" t="b">
+        <v>1</v>
+      </c>
+      <c r="O107" t="b">
+        <v>0</v>
+      </c>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="inlineStr"/>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5512,6 +7147,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N108" t="b">
+        <v>1</v>
+      </c>
+      <c r="O108" t="b">
+        <v>0</v>
+      </c>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="inlineStr"/>
+      <c r="U108" t="inlineStr"/>
+      <c r="V108" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5559,6 +7209,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N109" t="b">
+        <v>1</v>
+      </c>
+      <c r="O109" t="b">
+        <v>0</v>
+      </c>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr"/>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5606,6 +7271,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N110" t="b">
+        <v>1</v>
+      </c>
+      <c r="O110" t="b">
+        <v>0</v>
+      </c>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5653,6 +7333,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N111" t="b">
+        <v>1</v>
+      </c>
+      <c r="O111" t="b">
+        <v>0</v>
+      </c>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5700,6 +7395,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N112" t="b">
+        <v>1</v>
+      </c>
+      <c r="O112" t="b">
+        <v>0</v>
+      </c>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="inlineStr"/>
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5747,6 +7457,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N113" t="b">
+        <v>1</v>
+      </c>
+      <c r="O113" t="b">
+        <v>0</v>
+      </c>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr"/>
+      <c r="V113" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5794,6 +7519,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N114" t="b">
+        <v>1</v>
+      </c>
+      <c r="O114" t="b">
+        <v>0</v>
+      </c>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr"/>
+      <c r="V114" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5841,6 +7581,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N115" t="b">
+        <v>1</v>
+      </c>
+      <c r="O115" t="b">
+        <v>0</v>
+      </c>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr"/>
+      <c r="V115" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5888,6 +7643,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N116" t="b">
+        <v>1</v>
+      </c>
+      <c r="O116" t="b">
+        <v>0</v>
+      </c>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr"/>
+      <c r="V116" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5935,6 +7705,21 @@
           <t>['Много пропусков', 'Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N117" t="b">
+        <v>1</v>
+      </c>
+      <c r="O117" t="b">
+        <v>0</v>
+      </c>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr"/>
+      <c r="V117" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5982,6 +7767,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N118" t="b">
+        <v>1</v>
+      </c>
+      <c r="O118" t="b">
+        <v>0</v>
+      </c>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="inlineStr"/>
+      <c r="U118" t="inlineStr"/>
+      <c r="V118" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6029,6 +7829,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N119" t="b">
+        <v>1</v>
+      </c>
+      <c r="O119" t="b">
+        <v>0</v>
+      </c>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" t="inlineStr"/>
+      <c r="U119" t="inlineStr"/>
+      <c r="V119" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6076,6 +7891,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N120" t="b">
+        <v>1</v>
+      </c>
+      <c r="O120" t="b">
+        <v>0</v>
+      </c>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr"/>
+      <c r="V120" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6123,6 +7953,21 @@
           <t>['Много пропусков', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N121" t="b">
+        <v>1</v>
+      </c>
+      <c r="O121" t="b">
+        <v>0</v>
+      </c>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="inlineStr"/>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6170,6 +8015,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N122" t="b">
+        <v>1</v>
+      </c>
+      <c r="O122" t="b">
+        <v>0</v>
+      </c>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr"/>
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" t="inlineStr"/>
+      <c r="U122" t="inlineStr"/>
+      <c r="V122" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6217,6 +8077,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N123" t="b">
+        <v>1</v>
+      </c>
+      <c r="O123" t="b">
+        <v>0</v>
+      </c>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="inlineStr"/>
+      <c r="U123" t="inlineStr"/>
+      <c r="V123" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6265,6 +8140,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N124" t="b">
+        <v>1</v>
+      </c>
+      <c r="O124" t="b">
+        <v>0</v>
+      </c>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr"/>
+      <c r="T124" t="inlineStr"/>
+      <c r="U124" t="inlineStr"/>
+      <c r="V124" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6312,6 +8202,21 @@
           <t>['Константная колонка', 'Почти нет разброса', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N125" t="b">
+        <v>1</v>
+      </c>
+      <c r="O125" t="b">
+        <v>0</v>
+      </c>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr"/>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="inlineStr"/>
+      <c r="U125" t="inlineStr"/>
+      <c r="V125" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6359,6 +8264,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N126" t="b">
+        <v>1</v>
+      </c>
+      <c r="O126" t="b">
+        <v>0</v>
+      </c>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
+      <c r="S126" t="inlineStr"/>
+      <c r="T126" t="inlineStr"/>
+      <c r="U126" t="inlineStr"/>
+      <c r="V126" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6406,6 +8326,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N127" t="b">
+        <v>1</v>
+      </c>
+      <c r="O127" t="b">
+        <v>0</v>
+      </c>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr"/>
+      <c r="S127" t="inlineStr"/>
+      <c r="T127" t="inlineStr"/>
+      <c r="U127" t="inlineStr"/>
+      <c r="V127" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6453,6 +8388,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N128" t="b">
+        <v>1</v>
+      </c>
+      <c r="O128" t="b">
+        <v>0</v>
+      </c>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="inlineStr"/>
+      <c r="S128" t="inlineStr"/>
+      <c r="T128" t="inlineStr"/>
+      <c r="U128" t="inlineStr"/>
+      <c r="V128" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6500,6 +8450,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N129" t="b">
+        <v>1</v>
+      </c>
+      <c r="O129" t="b">
+        <v>0</v>
+      </c>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr"/>
+      <c r="S129" t="inlineStr"/>
+      <c r="T129" t="inlineStr"/>
+      <c r="U129" t="inlineStr"/>
+      <c r="V129" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6547,6 +8512,21 @@
           <t>['Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N130" t="b">
+        <v>1</v>
+      </c>
+      <c r="O130" t="b">
+        <v>0</v>
+      </c>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr"/>
+      <c r="S130" t="inlineStr"/>
+      <c r="T130" t="inlineStr"/>
+      <c r="U130" t="inlineStr"/>
+      <c r="V130" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6594,6 +8574,21 @@
           <t>['Константная колонка', 'Почти нет разброса', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N131" t="b">
+        <v>1</v>
+      </c>
+      <c r="O131" t="b">
+        <v>0</v>
+      </c>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr"/>
+      <c r="S131" t="inlineStr"/>
+      <c r="T131" t="inlineStr"/>
+      <c r="U131" t="inlineStr"/>
+      <c r="V131" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6641,6 +8636,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N132" t="b">
+        <v>1</v>
+      </c>
+      <c r="O132" t="b">
+        <v>0</v>
+      </c>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr"/>
+      <c r="S132" t="inlineStr"/>
+      <c r="T132" t="inlineStr"/>
+      <c r="U132" t="inlineStr"/>
+      <c r="V132" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6688,6 +8698,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N133" t="b">
+        <v>1</v>
+      </c>
+      <c r="O133" t="b">
+        <v>0</v>
+      </c>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr"/>
+      <c r="S133" t="inlineStr"/>
+      <c r="T133" t="inlineStr"/>
+      <c r="U133" t="inlineStr"/>
+      <c r="V133" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6735,6 +8760,21 @@
           <t>['Константная колонка', 'Почти нет разброса', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N134" t="b">
+        <v>1</v>
+      </c>
+      <c r="O134" t="b">
+        <v>0</v>
+      </c>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr"/>
+      <c r="S134" t="inlineStr"/>
+      <c r="T134" t="inlineStr"/>
+      <c r="U134" t="inlineStr"/>
+      <c r="V134" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6782,6 +8822,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N135" t="b">
+        <v>1</v>
+      </c>
+      <c r="O135" t="b">
+        <v>0</v>
+      </c>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr"/>
+      <c r="V135" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6829,6 +8884,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N136" t="b">
+        <v>1</v>
+      </c>
+      <c r="O136" t="b">
+        <v>0</v>
+      </c>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="inlineStr"/>
+      <c r="S136" t="inlineStr"/>
+      <c r="T136" t="inlineStr"/>
+      <c r="U136" t="inlineStr"/>
+      <c r="V136" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6876,6 +8946,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N137" t="b">
+        <v>1</v>
+      </c>
+      <c r="O137" t="b">
+        <v>0</v>
+      </c>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr"/>
+      <c r="S137" t="inlineStr"/>
+      <c r="T137" t="inlineStr"/>
+      <c r="U137" t="inlineStr"/>
+      <c r="V137" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6923,6 +9008,21 @@
           <t>['Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N138" t="b">
+        <v>1</v>
+      </c>
+      <c r="O138" t="b">
+        <v>0</v>
+      </c>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr"/>
+      <c r="S138" t="inlineStr"/>
+      <c r="T138" t="inlineStr"/>
+      <c r="U138" t="inlineStr"/>
+      <c r="V138" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6970,6 +9070,21 @@
           <t>['Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N139" t="b">
+        <v>1</v>
+      </c>
+      <c r="O139" t="b">
+        <v>0</v>
+      </c>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr"/>
+      <c r="S139" t="inlineStr"/>
+      <c r="T139" t="inlineStr"/>
+      <c r="U139" t="inlineStr"/>
+      <c r="V139" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7017,6 +9132,21 @@
           <t>['Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N140" t="b">
+        <v>1</v>
+      </c>
+      <c r="O140" t="b">
+        <v>0</v>
+      </c>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr"/>
+      <c r="S140" t="inlineStr"/>
+      <c r="T140" t="inlineStr"/>
+      <c r="U140" t="inlineStr"/>
+      <c r="V140" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7064,6 +9194,21 @@
           <t>['Константная колонка', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N141" t="b">
+        <v>1</v>
+      </c>
+      <c r="O141" t="b">
+        <v>0</v>
+      </c>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr"/>
+      <c r="S141" t="inlineStr"/>
+      <c r="T141" t="inlineStr"/>
+      <c r="U141" t="inlineStr"/>
+      <c r="V141" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7111,6 +9256,21 @@
           <t>['Константная колонка', 'Почти нет разброса', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N142" t="b">
+        <v>1</v>
+      </c>
+      <c r="O142" t="b">
+        <v>0</v>
+      </c>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr"/>
+      <c r="S142" t="inlineStr"/>
+      <c r="T142" t="inlineStr"/>
+      <c r="U142" t="inlineStr"/>
+      <c r="V142" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7158,6 +9318,21 @@
           <t>['Константная колонка', 'Почти нет разброса', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N143" t="b">
+        <v>1</v>
+      </c>
+      <c r="O143" t="b">
+        <v>0</v>
+      </c>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr"/>
+      <c r="S143" t="inlineStr"/>
+      <c r="T143" t="inlineStr"/>
+      <c r="U143" t="inlineStr"/>
+      <c r="V143" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7205,6 +9380,21 @@
           <t>['Константная колонка', 'Почти нет разброса', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N144" t="b">
+        <v>1</v>
+      </c>
+      <c r="O144" t="b">
+        <v>0</v>
+      </c>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr"/>
+      <c r="S144" t="inlineStr"/>
+      <c r="T144" t="inlineStr"/>
+      <c r="U144" t="inlineStr"/>
+      <c r="V144" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7252,6 +9442,21 @@
           <t>['Константная колонка', 'Почти нет разброса', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N145" t="b">
+        <v>1</v>
+      </c>
+      <c r="O145" t="b">
+        <v>0</v>
+      </c>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="inlineStr"/>
+      <c r="S145" t="inlineStr"/>
+      <c r="T145" t="inlineStr"/>
+      <c r="U145" t="inlineStr"/>
+      <c r="V145" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7299,6 +9504,21 @@
           <t>['Константная колонка', 'Почти нет разброса', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N146" t="b">
+        <v>1</v>
+      </c>
+      <c r="O146" t="b">
+        <v>0</v>
+      </c>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr"/>
+      <c r="S146" t="inlineStr"/>
+      <c r="T146" t="inlineStr"/>
+      <c r="U146" t="inlineStr"/>
+      <c r="V146" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7346,6 +9566,21 @@
           <t>['Константная колонка', 'Почти нет разброса', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N147" t="b">
+        <v>1</v>
+      </c>
+      <c r="O147" t="b">
+        <v>0</v>
+      </c>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr"/>
+      <c r="S147" t="inlineStr"/>
+      <c r="T147" t="inlineStr"/>
+      <c r="U147" t="inlineStr"/>
+      <c r="V147" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7393,6 +9628,21 @@
           <t>['Константная колонка', 'Почти нет разброса', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N148" t="b">
+        <v>1</v>
+      </c>
+      <c r="O148" t="b">
+        <v>0</v>
+      </c>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr"/>
+      <c r="R148" t="inlineStr"/>
+      <c r="S148" t="inlineStr"/>
+      <c r="T148" t="inlineStr"/>
+      <c r="U148" t="inlineStr"/>
+      <c r="V148" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7440,6 +9690,21 @@
           <t>['Константная колонка', 'Почти нет разброса', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N149" t="b">
+        <v>1</v>
+      </c>
+      <c r="O149" t="b">
+        <v>0</v>
+      </c>
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr"/>
+      <c r="S149" t="inlineStr"/>
+      <c r="T149" t="inlineStr"/>
+      <c r="U149" t="inlineStr"/>
+      <c r="V149" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7487,6 +9752,21 @@
           <t>['Константная колонка', 'Почти нет разброса', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N150" t="b">
+        <v>1</v>
+      </c>
+      <c r="O150" t="b">
+        <v>0</v>
+      </c>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr"/>
+      <c r="S150" t="inlineStr"/>
+      <c r="T150" t="inlineStr"/>
+      <c r="U150" t="inlineStr"/>
+      <c r="V150" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7534,6 +9814,21 @@
           <t>['Константная колонка', 'Почти нет разброса', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N151" t="b">
+        <v>1</v>
+      </c>
+      <c r="O151" t="b">
+        <v>0</v>
+      </c>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr"/>
+      <c r="S151" t="inlineStr"/>
+      <c r="T151" t="inlineStr"/>
+      <c r="U151" t="inlineStr"/>
+      <c r="V151" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7581,6 +9876,21 @@
           <t>['Константная колонка', 'Почти нет разброса', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N152" t="b">
+        <v>1</v>
+      </c>
+      <c r="O152" t="b">
+        <v>0</v>
+      </c>
+      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="inlineStr"/>
+      <c r="S152" t="inlineStr"/>
+      <c r="T152" t="inlineStr"/>
+      <c r="U152" t="inlineStr"/>
+      <c r="V152" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7628,6 +9938,21 @@
           <t>['Константная колонка', 'Почти нет разброса', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N153" t="b">
+        <v>1</v>
+      </c>
+      <c r="O153" t="b">
+        <v>0</v>
+      </c>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr"/>
+      <c r="S153" t="inlineStr"/>
+      <c r="T153" t="inlineStr"/>
+      <c r="U153" t="inlineStr"/>
+      <c r="V153" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7675,6 +10000,21 @@
           <t>['Константная колонка', 'Почти нет разброса', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N154" t="b">
+        <v>1</v>
+      </c>
+      <c r="O154" t="b">
+        <v>0</v>
+      </c>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr"/>
+      <c r="S154" t="inlineStr"/>
+      <c r="T154" t="inlineStr"/>
+      <c r="U154" t="inlineStr"/>
+      <c r="V154" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7722,6 +10062,21 @@
           <t>['Константная колонка', 'Почти нет разброса', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N155" t="b">
+        <v>1</v>
+      </c>
+      <c r="O155" t="b">
+        <v>0</v>
+      </c>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr"/>
+      <c r="S155" t="inlineStr"/>
+      <c r="T155" t="inlineStr"/>
+      <c r="U155" t="inlineStr"/>
+      <c r="V155" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7769,6 +10124,21 @@
           <t>['Константная колонка', 'Почти нет разброса', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N156" t="b">
+        <v>1</v>
+      </c>
+      <c r="O156" t="b">
+        <v>0</v>
+      </c>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr"/>
+      <c r="S156" t="inlineStr"/>
+      <c r="T156" t="inlineStr"/>
+      <c r="U156" t="inlineStr"/>
+      <c r="V156" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7816,6 +10186,21 @@
           <t>['Константная колонка', 'Почти нет разброса', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N157" t="b">
+        <v>1</v>
+      </c>
+      <c r="O157" t="b">
+        <v>0</v>
+      </c>
+      <c r="P157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr"/>
+      <c r="S157" t="inlineStr"/>
+      <c r="T157" t="inlineStr"/>
+      <c r="U157" t="inlineStr"/>
+      <c r="V157" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7863,6 +10248,21 @@
           <t>['Константная колонка', 'Почти нет разброса', 'Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N158" t="b">
+        <v>1</v>
+      </c>
+      <c r="O158" t="b">
+        <v>0</v>
+      </c>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="inlineStr"/>
+      <c r="S158" t="inlineStr"/>
+      <c r="T158" t="inlineStr"/>
+      <c r="U158" t="inlineStr"/>
+      <c r="V158" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7910,6 +10310,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N159" t="b">
+        <v>1</v>
+      </c>
+      <c r="O159" t="b">
+        <v>0</v>
+      </c>
+      <c r="P159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr"/>
+      <c r="S159" t="inlineStr"/>
+      <c r="T159" t="inlineStr"/>
+      <c r="U159" t="inlineStr"/>
+      <c r="V159" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7957,6 +10372,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N160" t="b">
+        <v>1</v>
+      </c>
+      <c r="O160" t="b">
+        <v>0</v>
+      </c>
+      <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr"/>
+      <c r="S160" t="inlineStr"/>
+      <c r="T160" t="inlineStr"/>
+      <c r="U160" t="inlineStr"/>
+      <c r="V160" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8004,6 +10434,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N161" t="b">
+        <v>1</v>
+      </c>
+      <c r="O161" t="b">
+        <v>0</v>
+      </c>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr"/>
+      <c r="R161" t="inlineStr"/>
+      <c r="S161" t="inlineStr"/>
+      <c r="T161" t="inlineStr"/>
+      <c r="U161" t="inlineStr"/>
+      <c r="V161" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8051,6 +10496,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N162" t="b">
+        <v>1</v>
+      </c>
+      <c r="O162" t="b">
+        <v>0</v>
+      </c>
+      <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr"/>
+      <c r="S162" t="inlineStr"/>
+      <c r="T162" t="inlineStr"/>
+      <c r="U162" t="inlineStr"/>
+      <c r="V162" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8098,6 +10558,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N163" t="b">
+        <v>1</v>
+      </c>
+      <c r="O163" t="b">
+        <v>0</v>
+      </c>
+      <c r="P163" t="inlineStr"/>
+      <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="inlineStr"/>
+      <c r="S163" t="inlineStr"/>
+      <c r="T163" t="inlineStr"/>
+      <c r="U163" t="inlineStr"/>
+      <c r="V163" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8145,6 +10620,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N164" t="b">
+        <v>1</v>
+      </c>
+      <c r="O164" t="b">
+        <v>0</v>
+      </c>
+      <c r="P164" t="inlineStr"/>
+      <c r="Q164" t="inlineStr"/>
+      <c r="R164" t="inlineStr"/>
+      <c r="S164" t="inlineStr"/>
+      <c r="T164" t="inlineStr"/>
+      <c r="U164" t="inlineStr"/>
+      <c r="V164" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8192,6 +10682,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N165" t="b">
+        <v>1</v>
+      </c>
+      <c r="O165" t="b">
+        <v>0</v>
+      </c>
+      <c r="P165" t="inlineStr"/>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr"/>
+      <c r="S165" t="inlineStr"/>
+      <c r="T165" t="inlineStr"/>
+      <c r="U165" t="inlineStr"/>
+      <c r="V165" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8239,6 +10744,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N166" t="b">
+        <v>1</v>
+      </c>
+      <c r="O166" t="b">
+        <v>0</v>
+      </c>
+      <c r="P166" t="inlineStr"/>
+      <c r="Q166" t="inlineStr"/>
+      <c r="R166" t="inlineStr"/>
+      <c r="S166" t="inlineStr"/>
+      <c r="T166" t="inlineStr"/>
+      <c r="U166" t="inlineStr"/>
+      <c r="V166" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8286,6 +10806,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N167" t="b">
+        <v>1</v>
+      </c>
+      <c r="O167" t="b">
+        <v>0</v>
+      </c>
+      <c r="P167" t="inlineStr"/>
+      <c r="Q167" t="inlineStr"/>
+      <c r="R167" t="inlineStr"/>
+      <c r="S167" t="inlineStr"/>
+      <c r="T167" t="inlineStr"/>
+      <c r="U167" t="inlineStr"/>
+      <c r="V167" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8333,6 +10868,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N168" t="b">
+        <v>1</v>
+      </c>
+      <c r="O168" t="b">
+        <v>0</v>
+      </c>
+      <c r="P168" t="inlineStr"/>
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="inlineStr"/>
+      <c r="S168" t="inlineStr"/>
+      <c r="T168" t="inlineStr"/>
+      <c r="U168" t="inlineStr"/>
+      <c r="V168" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8380,6 +10930,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N169" t="b">
+        <v>1</v>
+      </c>
+      <c r="O169" t="b">
+        <v>0</v>
+      </c>
+      <c r="P169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr"/>
+      <c r="S169" t="inlineStr"/>
+      <c r="T169" t="inlineStr"/>
+      <c r="U169" t="inlineStr"/>
+      <c r="V169" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8427,6 +10992,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N170" t="b">
+        <v>1</v>
+      </c>
+      <c r="O170" t="b">
+        <v>0</v>
+      </c>
+      <c r="P170" t="inlineStr"/>
+      <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="inlineStr"/>
+      <c r="S170" t="inlineStr"/>
+      <c r="T170" t="inlineStr"/>
+      <c r="U170" t="inlineStr"/>
+      <c r="V170" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8474,6 +11054,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N171" t="b">
+        <v>1</v>
+      </c>
+      <c r="O171" t="b">
+        <v>0</v>
+      </c>
+      <c r="P171" t="inlineStr"/>
+      <c r="Q171" t="inlineStr"/>
+      <c r="R171" t="inlineStr"/>
+      <c r="S171" t="inlineStr"/>
+      <c r="T171" t="inlineStr"/>
+      <c r="U171" t="inlineStr"/>
+      <c r="V171" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8521,6 +11116,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N172" t="b">
+        <v>1</v>
+      </c>
+      <c r="O172" t="b">
+        <v>0</v>
+      </c>
+      <c r="P172" t="inlineStr"/>
+      <c r="Q172" t="inlineStr"/>
+      <c r="R172" t="inlineStr"/>
+      <c r="S172" t="inlineStr"/>
+      <c r="T172" t="inlineStr"/>
+      <c r="U172" t="inlineStr"/>
+      <c r="V172" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8568,6 +11178,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N173" t="b">
+        <v>1</v>
+      </c>
+      <c r="O173" t="b">
+        <v>0</v>
+      </c>
+      <c r="P173" t="inlineStr"/>
+      <c r="Q173" t="inlineStr"/>
+      <c r="R173" t="inlineStr"/>
+      <c r="S173" t="inlineStr"/>
+      <c r="T173" t="inlineStr"/>
+      <c r="U173" t="inlineStr"/>
+      <c r="V173" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8615,6 +11240,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N174" t="b">
+        <v>1</v>
+      </c>
+      <c r="O174" t="b">
+        <v>0</v>
+      </c>
+      <c r="P174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="inlineStr"/>
+      <c r="S174" t="inlineStr"/>
+      <c r="T174" t="inlineStr"/>
+      <c r="U174" t="inlineStr"/>
+      <c r="V174" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8662,6 +11302,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N175" t="b">
+        <v>1</v>
+      </c>
+      <c r="O175" t="b">
+        <v>0</v>
+      </c>
+      <c r="P175" t="inlineStr"/>
+      <c r="Q175" t="inlineStr"/>
+      <c r="R175" t="inlineStr"/>
+      <c r="S175" t="inlineStr"/>
+      <c r="T175" t="inlineStr"/>
+      <c r="U175" t="inlineStr"/>
+      <c r="V175" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8709,6 +11364,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N176" t="b">
+        <v>1</v>
+      </c>
+      <c r="O176" t="b">
+        <v>0</v>
+      </c>
+      <c r="P176" t="inlineStr"/>
+      <c r="Q176" t="inlineStr"/>
+      <c r="R176" t="inlineStr"/>
+      <c r="S176" t="inlineStr"/>
+      <c r="T176" t="inlineStr"/>
+      <c r="U176" t="inlineStr"/>
+      <c r="V176" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8756,6 +11426,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N177" t="b">
+        <v>1</v>
+      </c>
+      <c r="O177" t="b">
+        <v>0</v>
+      </c>
+      <c r="P177" t="inlineStr"/>
+      <c r="Q177" t="inlineStr"/>
+      <c r="R177" t="inlineStr"/>
+      <c r="S177" t="inlineStr"/>
+      <c r="T177" t="inlineStr"/>
+      <c r="U177" t="inlineStr"/>
+      <c r="V177" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -8803,6 +11488,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N178" t="b">
+        <v>1</v>
+      </c>
+      <c r="O178" t="b">
+        <v>0</v>
+      </c>
+      <c r="P178" t="inlineStr"/>
+      <c r="Q178" t="inlineStr"/>
+      <c r="R178" t="inlineStr"/>
+      <c r="S178" t="inlineStr"/>
+      <c r="T178" t="inlineStr"/>
+      <c r="U178" t="inlineStr"/>
+      <c r="V178" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8850,6 +11550,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N179" t="b">
+        <v>1</v>
+      </c>
+      <c r="O179" t="b">
+        <v>0</v>
+      </c>
+      <c r="P179" t="inlineStr"/>
+      <c r="Q179" t="inlineStr"/>
+      <c r="R179" t="inlineStr"/>
+      <c r="S179" t="inlineStr"/>
+      <c r="T179" t="inlineStr"/>
+      <c r="U179" t="inlineStr"/>
+      <c r="V179" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -8897,6 +11612,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N180" t="b">
+        <v>1</v>
+      </c>
+      <c r="O180" t="b">
+        <v>0</v>
+      </c>
+      <c r="P180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="inlineStr"/>
+      <c r="S180" t="inlineStr"/>
+      <c r="T180" t="inlineStr"/>
+      <c r="U180" t="inlineStr"/>
+      <c r="V180" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -8944,6 +11674,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N181" t="b">
+        <v>1</v>
+      </c>
+      <c r="O181" t="b">
+        <v>0</v>
+      </c>
+      <c r="P181" t="inlineStr"/>
+      <c r="Q181" t="inlineStr"/>
+      <c r="R181" t="inlineStr"/>
+      <c r="S181" t="inlineStr"/>
+      <c r="T181" t="inlineStr"/>
+      <c r="U181" t="inlineStr"/>
+      <c r="V181" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -8991,6 +11736,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N182" t="b">
+        <v>1</v>
+      </c>
+      <c r="O182" t="b">
+        <v>0</v>
+      </c>
+      <c r="P182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr"/>
+      <c r="R182" t="inlineStr"/>
+      <c r="S182" t="inlineStr"/>
+      <c r="T182" t="inlineStr"/>
+      <c r="U182" t="inlineStr"/>
+      <c r="V182" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9038,6 +11798,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N183" t="b">
+        <v>1</v>
+      </c>
+      <c r="O183" t="b">
+        <v>0</v>
+      </c>
+      <c r="P183" t="inlineStr"/>
+      <c r="Q183" t="inlineStr"/>
+      <c r="R183" t="inlineStr"/>
+      <c r="S183" t="inlineStr"/>
+      <c r="T183" t="inlineStr"/>
+      <c r="U183" t="inlineStr"/>
+      <c r="V183" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -9085,6 +11860,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N184" t="b">
+        <v>1</v>
+      </c>
+      <c r="O184" t="b">
+        <v>0</v>
+      </c>
+      <c r="P184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr"/>
+      <c r="R184" t="inlineStr"/>
+      <c r="S184" t="inlineStr"/>
+      <c r="T184" t="inlineStr"/>
+      <c r="U184" t="inlineStr"/>
+      <c r="V184" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -9132,6 +11922,21 @@
           <t>['Почти всегда одно и то же значение']</t>
         </is>
       </c>
+      <c r="N185" t="b">
+        <v>1</v>
+      </c>
+      <c r="O185" t="b">
+        <v>0</v>
+      </c>
+      <c r="P185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="inlineStr"/>
+      <c r="S185" t="inlineStr"/>
+      <c r="T185" t="inlineStr"/>
+      <c r="U185" t="inlineStr"/>
+      <c r="V185" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9179,6 +11984,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N186" t="b">
+        <v>0</v>
+      </c>
+      <c r="O186" t="b">
+        <v>0</v>
+      </c>
+      <c r="P186" t="inlineStr"/>
+      <c r="Q186" t="inlineStr"/>
+      <c r="R186" t="inlineStr"/>
+      <c r="S186" t="inlineStr"/>
+      <c r="T186" t="inlineStr"/>
+      <c r="U186" t="inlineStr"/>
+      <c r="V186" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9226,6 +12046,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N187" t="b">
+        <v>0</v>
+      </c>
+      <c r="O187" t="b">
+        <v>0</v>
+      </c>
+      <c r="P187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr"/>
+      <c r="R187" t="inlineStr"/>
+      <c r="S187" t="inlineStr"/>
+      <c r="T187" t="inlineStr"/>
+      <c r="U187" t="inlineStr"/>
+      <c r="V187" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9273,6 +12108,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N188" t="b">
+        <v>0</v>
+      </c>
+      <c r="O188" t="b">
+        <v>0</v>
+      </c>
+      <c r="P188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="inlineStr"/>
+      <c r="S188" t="inlineStr"/>
+      <c r="T188" t="inlineStr"/>
+      <c r="U188" t="inlineStr"/>
+      <c r="V188" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9320,6 +12170,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N189" t="b">
+        <v>0</v>
+      </c>
+      <c r="O189" t="b">
+        <v>0</v>
+      </c>
+      <c r="P189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr"/>
+      <c r="S189" t="inlineStr"/>
+      <c r="T189" t="inlineStr"/>
+      <c r="U189" t="inlineStr"/>
+      <c r="V189" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -9367,6 +12232,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N190" t="b">
+        <v>0</v>
+      </c>
+      <c r="O190" t="b">
+        <v>0</v>
+      </c>
+      <c r="P190" t="inlineStr"/>
+      <c r="Q190" t="inlineStr"/>
+      <c r="R190" t="inlineStr"/>
+      <c r="S190" t="inlineStr"/>
+      <c r="T190" t="inlineStr"/>
+      <c r="U190" t="inlineStr"/>
+      <c r="V190" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -9414,6 +12294,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N191" t="b">
+        <v>0</v>
+      </c>
+      <c r="O191" t="b">
+        <v>0</v>
+      </c>
+      <c r="P191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr"/>
+      <c r="R191" t="inlineStr"/>
+      <c r="S191" t="inlineStr"/>
+      <c r="T191" t="inlineStr"/>
+      <c r="U191" t="inlineStr"/>
+      <c r="V191" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -9461,6 +12356,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N192" t="b">
+        <v>0</v>
+      </c>
+      <c r="O192" t="b">
+        <v>0</v>
+      </c>
+      <c r="P192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="inlineStr"/>
+      <c r="S192" t="inlineStr"/>
+      <c r="T192" t="inlineStr"/>
+      <c r="U192" t="inlineStr"/>
+      <c r="V192" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -9508,6 +12418,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N193" t="b">
+        <v>0</v>
+      </c>
+      <c r="O193" t="b">
+        <v>0</v>
+      </c>
+      <c r="P193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr"/>
+      <c r="R193" t="inlineStr"/>
+      <c r="S193" t="inlineStr"/>
+      <c r="T193" t="inlineStr"/>
+      <c r="U193" t="inlineStr"/>
+      <c r="V193" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -9555,6 +12480,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N194" t="b">
+        <v>0</v>
+      </c>
+      <c r="O194" t="b">
+        <v>0</v>
+      </c>
+      <c r="P194" t="inlineStr"/>
+      <c r="Q194" t="inlineStr"/>
+      <c r="R194" t="inlineStr"/>
+      <c r="S194" t="inlineStr"/>
+      <c r="T194" t="inlineStr"/>
+      <c r="U194" t="inlineStr"/>
+      <c r="V194" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9602,6 +12542,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N195" t="b">
+        <v>0</v>
+      </c>
+      <c r="O195" t="b">
+        <v>0</v>
+      </c>
+      <c r="P195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr"/>
+      <c r="R195" t="inlineStr"/>
+      <c r="S195" t="inlineStr"/>
+      <c r="T195" t="inlineStr"/>
+      <c r="U195" t="inlineStr"/>
+      <c r="V195" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -9649,6 +12604,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N196" t="b">
+        <v>0</v>
+      </c>
+      <c r="O196" t="b">
+        <v>0</v>
+      </c>
+      <c r="P196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr"/>
+      <c r="R196" t="inlineStr"/>
+      <c r="S196" t="inlineStr"/>
+      <c r="T196" t="inlineStr"/>
+      <c r="U196" t="inlineStr"/>
+      <c r="V196" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -9696,6 +12666,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N197" t="b">
+        <v>0</v>
+      </c>
+      <c r="O197" t="b">
+        <v>0</v>
+      </c>
+      <c r="P197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr"/>
+      <c r="R197" t="inlineStr"/>
+      <c r="S197" t="inlineStr"/>
+      <c r="T197" t="inlineStr"/>
+      <c r="U197" t="inlineStr"/>
+      <c r="V197" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -9743,6 +12728,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N198" t="b">
+        <v>0</v>
+      </c>
+      <c r="O198" t="b">
+        <v>0</v>
+      </c>
+      <c r="P198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="inlineStr"/>
+      <c r="S198" t="inlineStr"/>
+      <c r="T198" t="inlineStr"/>
+      <c r="U198" t="inlineStr"/>
+      <c r="V198" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -9790,6 +12790,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N199" t="b">
+        <v>0</v>
+      </c>
+      <c r="O199" t="b">
+        <v>0</v>
+      </c>
+      <c r="P199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr"/>
+      <c r="R199" t="inlineStr"/>
+      <c r="S199" t="inlineStr"/>
+      <c r="T199" t="inlineStr"/>
+      <c r="U199" t="inlineStr"/>
+      <c r="V199" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -9837,6 +12852,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N200" t="b">
+        <v>0</v>
+      </c>
+      <c r="O200" t="b">
+        <v>0</v>
+      </c>
+      <c r="P200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr"/>
+      <c r="R200" t="inlineStr"/>
+      <c r="S200" t="inlineStr"/>
+      <c r="T200" t="inlineStr"/>
+      <c r="U200" t="inlineStr"/>
+      <c r="V200" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -9884,6 +12914,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N201" t="b">
+        <v>0</v>
+      </c>
+      <c r="O201" t="b">
+        <v>0</v>
+      </c>
+      <c r="P201" t="inlineStr"/>
+      <c r="Q201" t="inlineStr"/>
+      <c r="R201" t="inlineStr"/>
+      <c r="S201" t="inlineStr"/>
+      <c r="T201" t="inlineStr"/>
+      <c r="U201" t="inlineStr"/>
+      <c r="V201" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -9931,6 +12976,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N202" t="b">
+        <v>0</v>
+      </c>
+      <c r="O202" t="b">
+        <v>0</v>
+      </c>
+      <c r="P202" t="inlineStr"/>
+      <c r="Q202" t="inlineStr"/>
+      <c r="R202" t="inlineStr"/>
+      <c r="S202" t="inlineStr"/>
+      <c r="T202" t="inlineStr"/>
+      <c r="U202" t="inlineStr"/>
+      <c r="V202" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -9978,6 +13038,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N203" t="b">
+        <v>0</v>
+      </c>
+      <c r="O203" t="b">
+        <v>0</v>
+      </c>
+      <c r="P203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
+      <c r="R203" t="inlineStr"/>
+      <c r="S203" t="inlineStr"/>
+      <c r="T203" t="inlineStr"/>
+      <c r="U203" t="inlineStr"/>
+      <c r="V203" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -10025,6 +13100,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N204" t="b">
+        <v>0</v>
+      </c>
+      <c r="O204" t="b">
+        <v>0</v>
+      </c>
+      <c r="P204" t="inlineStr"/>
+      <c r="Q204" t="inlineStr"/>
+      <c r="R204" t="inlineStr"/>
+      <c r="S204" t="inlineStr"/>
+      <c r="T204" t="inlineStr"/>
+      <c r="U204" t="inlineStr"/>
+      <c r="V204" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -10072,6 +13162,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N205" t="b">
+        <v>0</v>
+      </c>
+      <c r="O205" t="b">
+        <v>0</v>
+      </c>
+      <c r="P205" t="inlineStr"/>
+      <c r="Q205" t="inlineStr"/>
+      <c r="R205" t="inlineStr"/>
+      <c r="S205" t="inlineStr"/>
+      <c r="T205" t="inlineStr"/>
+      <c r="U205" t="inlineStr"/>
+      <c r="V205" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -10119,6 +13224,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N206" t="b">
+        <v>0</v>
+      </c>
+      <c r="O206" t="b">
+        <v>0</v>
+      </c>
+      <c r="P206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr"/>
+      <c r="R206" t="inlineStr"/>
+      <c r="S206" t="inlineStr"/>
+      <c r="T206" t="inlineStr"/>
+      <c r="U206" t="inlineStr"/>
+      <c r="V206" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -10166,6 +13286,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N207" t="b">
+        <v>0</v>
+      </c>
+      <c r="O207" t="b">
+        <v>0</v>
+      </c>
+      <c r="P207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="inlineStr"/>
+      <c r="S207" t="inlineStr"/>
+      <c r="T207" t="inlineStr"/>
+      <c r="U207" t="inlineStr"/>
+      <c r="V207" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -10213,6 +13348,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N208" t="b">
+        <v>0</v>
+      </c>
+      <c r="O208" t="b">
+        <v>0</v>
+      </c>
+      <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="inlineStr"/>
+      <c r="S208" t="inlineStr"/>
+      <c r="T208" t="inlineStr"/>
+      <c r="U208" t="inlineStr"/>
+      <c r="V208" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -10260,6 +13410,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N209" t="b">
+        <v>0</v>
+      </c>
+      <c r="O209" t="b">
+        <v>0</v>
+      </c>
+      <c r="P209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr"/>
+      <c r="R209" t="inlineStr"/>
+      <c r="S209" t="inlineStr"/>
+      <c r="T209" t="inlineStr"/>
+      <c r="U209" t="inlineStr"/>
+      <c r="V209" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -10307,6 +13472,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N210" t="b">
+        <v>0</v>
+      </c>
+      <c r="O210" t="b">
+        <v>0</v>
+      </c>
+      <c r="P210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr"/>
+      <c r="R210" t="inlineStr"/>
+      <c r="S210" t="inlineStr"/>
+      <c r="T210" t="inlineStr"/>
+      <c r="U210" t="inlineStr"/>
+      <c r="V210" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -10354,6 +13534,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N211" t="b">
+        <v>0</v>
+      </c>
+      <c r="O211" t="b">
+        <v>0</v>
+      </c>
+      <c r="P211" t="inlineStr"/>
+      <c r="Q211" t="inlineStr"/>
+      <c r="R211" t="inlineStr"/>
+      <c r="S211" t="inlineStr"/>
+      <c r="T211" t="inlineStr"/>
+      <c r="U211" t="inlineStr"/>
+      <c r="V211" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -10401,6 +13596,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N212" t="b">
+        <v>0</v>
+      </c>
+      <c r="O212" t="b">
+        <v>0</v>
+      </c>
+      <c r="P212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="inlineStr"/>
+      <c r="S212" t="inlineStr"/>
+      <c r="T212" t="inlineStr"/>
+      <c r="U212" t="inlineStr"/>
+      <c r="V212" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -10448,6 +13658,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N213" t="b">
+        <v>0</v>
+      </c>
+      <c r="O213" t="b">
+        <v>0</v>
+      </c>
+      <c r="P213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr"/>
+      <c r="R213" t="inlineStr"/>
+      <c r="S213" t="inlineStr"/>
+      <c r="T213" t="inlineStr"/>
+      <c r="U213" t="inlineStr"/>
+      <c r="V213" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -10495,6 +13720,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N214" t="b">
+        <v>0</v>
+      </c>
+      <c r="O214" t="b">
+        <v>0</v>
+      </c>
+      <c r="P214" t="inlineStr"/>
+      <c r="Q214" t="inlineStr"/>
+      <c r="R214" t="inlineStr"/>
+      <c r="S214" t="inlineStr"/>
+      <c r="T214" t="inlineStr"/>
+      <c r="U214" t="inlineStr"/>
+      <c r="V214" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -10542,6 +13782,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N215" t="b">
+        <v>0</v>
+      </c>
+      <c r="O215" t="b">
+        <v>0</v>
+      </c>
+      <c r="P215" t="inlineStr"/>
+      <c r="Q215" t="inlineStr"/>
+      <c r="R215" t="inlineStr"/>
+      <c r="S215" t="inlineStr"/>
+      <c r="T215" t="inlineStr"/>
+      <c r="U215" t="inlineStr"/>
+      <c r="V215" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -10589,6 +13844,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N216" t="b">
+        <v>0</v>
+      </c>
+      <c r="O216" t="b">
+        <v>0</v>
+      </c>
+      <c r="P216" t="inlineStr"/>
+      <c r="Q216" t="inlineStr"/>
+      <c r="R216" t="inlineStr"/>
+      <c r="S216" t="inlineStr"/>
+      <c r="T216" t="inlineStr"/>
+      <c r="U216" t="inlineStr"/>
+      <c r="V216" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -10636,6 +13906,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N217" t="b">
+        <v>0</v>
+      </c>
+      <c r="O217" t="b">
+        <v>0</v>
+      </c>
+      <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr"/>
+      <c r="R217" t="inlineStr"/>
+      <c r="S217" t="inlineStr"/>
+      <c r="T217" t="inlineStr"/>
+      <c r="U217" t="inlineStr"/>
+      <c r="V217" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -10683,6 +13968,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N218" t="b">
+        <v>0</v>
+      </c>
+      <c r="O218" t="b">
+        <v>0</v>
+      </c>
+      <c r="P218" t="inlineStr"/>
+      <c r="Q218" t="inlineStr"/>
+      <c r="R218" t="inlineStr"/>
+      <c r="S218" t="inlineStr"/>
+      <c r="T218" t="inlineStr"/>
+      <c r="U218" t="inlineStr"/>
+      <c r="V218" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -10730,6 +14030,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N219" t="b">
+        <v>0</v>
+      </c>
+      <c r="O219" t="b">
+        <v>0</v>
+      </c>
+      <c r="P219" t="inlineStr"/>
+      <c r="Q219" t="inlineStr"/>
+      <c r="R219" t="inlineStr"/>
+      <c r="S219" t="inlineStr"/>
+      <c r="T219" t="inlineStr"/>
+      <c r="U219" t="inlineStr"/>
+      <c r="V219" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -10777,6 +14092,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N220" t="b">
+        <v>0</v>
+      </c>
+      <c r="O220" t="b">
+        <v>0</v>
+      </c>
+      <c r="P220" t="inlineStr"/>
+      <c r="Q220" t="inlineStr"/>
+      <c r="R220" t="inlineStr"/>
+      <c r="S220" t="inlineStr"/>
+      <c r="T220" t="inlineStr"/>
+      <c r="U220" t="inlineStr"/>
+      <c r="V220" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -10824,6 +14154,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N221" t="b">
+        <v>0</v>
+      </c>
+      <c r="O221" t="b">
+        <v>0</v>
+      </c>
+      <c r="P221" t="inlineStr"/>
+      <c r="Q221" t="inlineStr"/>
+      <c r="R221" t="inlineStr"/>
+      <c r="S221" t="inlineStr"/>
+      <c r="T221" t="inlineStr"/>
+      <c r="U221" t="inlineStr"/>
+      <c r="V221" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -10871,6 +14216,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N222" t="b">
+        <v>0</v>
+      </c>
+      <c r="O222" t="b">
+        <v>0</v>
+      </c>
+      <c r="P222" t="inlineStr"/>
+      <c r="Q222" t="inlineStr"/>
+      <c r="R222" t="inlineStr"/>
+      <c r="S222" t="inlineStr"/>
+      <c r="T222" t="inlineStr"/>
+      <c r="U222" t="inlineStr"/>
+      <c r="V222" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -10918,6 +14278,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N223" t="b">
+        <v>0</v>
+      </c>
+      <c r="O223" t="b">
+        <v>0</v>
+      </c>
+      <c r="P223" t="inlineStr"/>
+      <c r="Q223" t="inlineStr"/>
+      <c r="R223" t="inlineStr"/>
+      <c r="S223" t="inlineStr"/>
+      <c r="T223" t="inlineStr"/>
+      <c r="U223" t="inlineStr"/>
+      <c r="V223" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -10965,6 +14340,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N224" t="b">
+        <v>0</v>
+      </c>
+      <c r="O224" t="b">
+        <v>0</v>
+      </c>
+      <c r="P224" t="inlineStr"/>
+      <c r="Q224" t="inlineStr"/>
+      <c r="R224" t="inlineStr"/>
+      <c r="S224" t="inlineStr"/>
+      <c r="T224" t="inlineStr"/>
+      <c r="U224" t="inlineStr"/>
+      <c r="V224" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -11012,6 +14402,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N225" t="b">
+        <v>0</v>
+      </c>
+      <c r="O225" t="b">
+        <v>0</v>
+      </c>
+      <c r="P225" t="inlineStr"/>
+      <c r="Q225" t="inlineStr"/>
+      <c r="R225" t="inlineStr"/>
+      <c r="S225" t="inlineStr"/>
+      <c r="T225" t="inlineStr"/>
+      <c r="U225" t="inlineStr"/>
+      <c r="V225" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -11059,6 +14464,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N226" t="b">
+        <v>0</v>
+      </c>
+      <c r="O226" t="b">
+        <v>0</v>
+      </c>
+      <c r="P226" t="inlineStr"/>
+      <c r="Q226" t="inlineStr"/>
+      <c r="R226" t="inlineStr"/>
+      <c r="S226" t="inlineStr"/>
+      <c r="T226" t="inlineStr"/>
+      <c r="U226" t="inlineStr"/>
+      <c r="V226" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -11106,6 +14526,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N227" t="b">
+        <v>0</v>
+      </c>
+      <c r="O227" t="b">
+        <v>0</v>
+      </c>
+      <c r="P227" t="inlineStr"/>
+      <c r="Q227" t="inlineStr"/>
+      <c r="R227" t="inlineStr"/>
+      <c r="S227" t="inlineStr"/>
+      <c r="T227" t="inlineStr"/>
+      <c r="U227" t="inlineStr"/>
+      <c r="V227" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -11153,6 +14588,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N228" t="b">
+        <v>0</v>
+      </c>
+      <c r="O228" t="b">
+        <v>0</v>
+      </c>
+      <c r="P228" t="inlineStr"/>
+      <c r="Q228" t="inlineStr"/>
+      <c r="R228" t="inlineStr"/>
+      <c r="S228" t="inlineStr"/>
+      <c r="T228" t="inlineStr"/>
+      <c r="U228" t="inlineStr"/>
+      <c r="V228" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -11200,6 +14650,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N229" t="b">
+        <v>0</v>
+      </c>
+      <c r="O229" t="b">
+        <v>0</v>
+      </c>
+      <c r="P229" t="inlineStr"/>
+      <c r="Q229" t="inlineStr"/>
+      <c r="R229" t="inlineStr"/>
+      <c r="S229" t="inlineStr"/>
+      <c r="T229" t="inlineStr"/>
+      <c r="U229" t="inlineStr"/>
+      <c r="V229" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -11247,6 +14712,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N230" t="b">
+        <v>0</v>
+      </c>
+      <c r="O230" t="b">
+        <v>0</v>
+      </c>
+      <c r="P230" t="inlineStr"/>
+      <c r="Q230" t="inlineStr"/>
+      <c r="R230" t="inlineStr"/>
+      <c r="S230" t="inlineStr"/>
+      <c r="T230" t="inlineStr"/>
+      <c r="U230" t="inlineStr"/>
+      <c r="V230" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -11294,6 +14774,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N231" t="b">
+        <v>0</v>
+      </c>
+      <c r="O231" t="b">
+        <v>0</v>
+      </c>
+      <c r="P231" t="inlineStr"/>
+      <c r="Q231" t="inlineStr"/>
+      <c r="R231" t="inlineStr"/>
+      <c r="S231" t="inlineStr"/>
+      <c r="T231" t="inlineStr"/>
+      <c r="U231" t="inlineStr"/>
+      <c r="V231" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -11341,6 +14836,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N232" t="b">
+        <v>0</v>
+      </c>
+      <c r="O232" t="b">
+        <v>0</v>
+      </c>
+      <c r="P232" t="inlineStr"/>
+      <c r="Q232" t="inlineStr"/>
+      <c r="R232" t="inlineStr"/>
+      <c r="S232" t="inlineStr"/>
+      <c r="T232" t="inlineStr"/>
+      <c r="U232" t="inlineStr"/>
+      <c r="V232" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -11388,6 +14898,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N233" t="b">
+        <v>0</v>
+      </c>
+      <c r="O233" t="b">
+        <v>0</v>
+      </c>
+      <c r="P233" t="inlineStr"/>
+      <c r="Q233" t="inlineStr"/>
+      <c r="R233" t="inlineStr"/>
+      <c r="S233" t="inlineStr"/>
+      <c r="T233" t="inlineStr"/>
+      <c r="U233" t="inlineStr"/>
+      <c r="V233" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -11435,6 +14960,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N234" t="b">
+        <v>0</v>
+      </c>
+      <c r="O234" t="b">
+        <v>0</v>
+      </c>
+      <c r="P234" t="inlineStr"/>
+      <c r="Q234" t="inlineStr"/>
+      <c r="R234" t="inlineStr"/>
+      <c r="S234" t="inlineStr"/>
+      <c r="T234" t="inlineStr"/>
+      <c r="U234" t="inlineStr"/>
+      <c r="V234" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -11482,6 +15022,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N235" t="b">
+        <v>0</v>
+      </c>
+      <c r="O235" t="b">
+        <v>0</v>
+      </c>
+      <c r="P235" t="inlineStr"/>
+      <c r="Q235" t="inlineStr"/>
+      <c r="R235" t="inlineStr"/>
+      <c r="S235" t="inlineStr"/>
+      <c r="T235" t="inlineStr"/>
+      <c r="U235" t="inlineStr"/>
+      <c r="V235" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -11529,6 +15084,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N236" t="b">
+        <v>0</v>
+      </c>
+      <c r="O236" t="b">
+        <v>0</v>
+      </c>
+      <c r="P236" t="inlineStr"/>
+      <c r="Q236" t="inlineStr"/>
+      <c r="R236" t="inlineStr"/>
+      <c r="S236" t="inlineStr"/>
+      <c r="T236" t="inlineStr"/>
+      <c r="U236" t="inlineStr"/>
+      <c r="V236" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -11576,6 +15146,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N237" t="b">
+        <v>0</v>
+      </c>
+      <c r="O237" t="b">
+        <v>0</v>
+      </c>
+      <c r="P237" t="inlineStr"/>
+      <c r="Q237" t="inlineStr"/>
+      <c r="R237" t="inlineStr"/>
+      <c r="S237" t="inlineStr"/>
+      <c r="T237" t="inlineStr"/>
+      <c r="U237" t="inlineStr"/>
+      <c r="V237" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -11623,6 +15208,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N238" t="b">
+        <v>0</v>
+      </c>
+      <c r="O238" t="b">
+        <v>0</v>
+      </c>
+      <c r="P238" t="inlineStr"/>
+      <c r="Q238" t="inlineStr"/>
+      <c r="R238" t="inlineStr"/>
+      <c r="S238" t="inlineStr"/>
+      <c r="T238" t="inlineStr"/>
+      <c r="U238" t="inlineStr"/>
+      <c r="V238" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -11670,6 +15270,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N239" t="b">
+        <v>0</v>
+      </c>
+      <c r="O239" t="b">
+        <v>0</v>
+      </c>
+      <c r="P239" t="inlineStr"/>
+      <c r="Q239" t="inlineStr"/>
+      <c r="R239" t="inlineStr"/>
+      <c r="S239" t="inlineStr"/>
+      <c r="T239" t="inlineStr"/>
+      <c r="U239" t="inlineStr"/>
+      <c r="V239" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -11717,6 +15332,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N240" t="b">
+        <v>0</v>
+      </c>
+      <c r="O240" t="b">
+        <v>0</v>
+      </c>
+      <c r="P240" t="inlineStr"/>
+      <c r="Q240" t="inlineStr"/>
+      <c r="R240" t="inlineStr"/>
+      <c r="S240" t="inlineStr"/>
+      <c r="T240" t="inlineStr"/>
+      <c r="U240" t="inlineStr"/>
+      <c r="V240" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -11764,6 +15394,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N241" t="b">
+        <v>0</v>
+      </c>
+      <c r="O241" t="b">
+        <v>0</v>
+      </c>
+      <c r="P241" t="inlineStr"/>
+      <c r="Q241" t="inlineStr"/>
+      <c r="R241" t="inlineStr"/>
+      <c r="S241" t="inlineStr"/>
+      <c r="T241" t="inlineStr"/>
+      <c r="U241" t="inlineStr"/>
+      <c r="V241" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -11811,6 +15456,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N242" t="b">
+        <v>0</v>
+      </c>
+      <c r="O242" t="b">
+        <v>0</v>
+      </c>
+      <c r="P242" t="inlineStr"/>
+      <c r="Q242" t="inlineStr"/>
+      <c r="R242" t="inlineStr"/>
+      <c r="S242" t="inlineStr"/>
+      <c r="T242" t="inlineStr"/>
+      <c r="U242" t="inlineStr"/>
+      <c r="V242" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -11858,6 +15518,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N243" t="b">
+        <v>0</v>
+      </c>
+      <c r="O243" t="b">
+        <v>0</v>
+      </c>
+      <c r="P243" t="inlineStr"/>
+      <c r="Q243" t="inlineStr"/>
+      <c r="R243" t="inlineStr"/>
+      <c r="S243" t="inlineStr"/>
+      <c r="T243" t="inlineStr"/>
+      <c r="U243" t="inlineStr"/>
+      <c r="V243" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -11905,6 +15580,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N244" t="b">
+        <v>0</v>
+      </c>
+      <c r="O244" t="b">
+        <v>0</v>
+      </c>
+      <c r="P244" t="inlineStr"/>
+      <c r="Q244" t="inlineStr"/>
+      <c r="R244" t="inlineStr"/>
+      <c r="S244" t="inlineStr"/>
+      <c r="T244" t="inlineStr"/>
+      <c r="U244" t="inlineStr"/>
+      <c r="V244" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -11952,6 +15642,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N245" t="b">
+        <v>0</v>
+      </c>
+      <c r="O245" t="b">
+        <v>0</v>
+      </c>
+      <c r="P245" t="inlineStr"/>
+      <c r="Q245" t="inlineStr"/>
+      <c r="R245" t="inlineStr"/>
+      <c r="S245" t="inlineStr"/>
+      <c r="T245" t="inlineStr"/>
+      <c r="U245" t="inlineStr"/>
+      <c r="V245" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -11999,6 +15704,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N246" t="b">
+        <v>0</v>
+      </c>
+      <c r="O246" t="b">
+        <v>0</v>
+      </c>
+      <c r="P246" t="inlineStr"/>
+      <c r="Q246" t="inlineStr"/>
+      <c r="R246" t="inlineStr"/>
+      <c r="S246" t="inlineStr"/>
+      <c r="T246" t="inlineStr"/>
+      <c r="U246" t="inlineStr"/>
+      <c r="V246" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -12046,6 +15766,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N247" t="b">
+        <v>0</v>
+      </c>
+      <c r="O247" t="b">
+        <v>0</v>
+      </c>
+      <c r="P247" t="inlineStr"/>
+      <c r="Q247" t="inlineStr"/>
+      <c r="R247" t="inlineStr"/>
+      <c r="S247" t="inlineStr"/>
+      <c r="T247" t="inlineStr"/>
+      <c r="U247" t="inlineStr"/>
+      <c r="V247" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -12093,6 +15828,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N248" t="b">
+        <v>0</v>
+      </c>
+      <c r="O248" t="b">
+        <v>0</v>
+      </c>
+      <c r="P248" t="inlineStr"/>
+      <c r="Q248" t="inlineStr"/>
+      <c r="R248" t="inlineStr"/>
+      <c r="S248" t="inlineStr"/>
+      <c r="T248" t="inlineStr"/>
+      <c r="U248" t="inlineStr"/>
+      <c r="V248" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -12140,6 +15890,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N249" t="b">
+        <v>0</v>
+      </c>
+      <c r="O249" t="b">
+        <v>0</v>
+      </c>
+      <c r="P249" t="inlineStr"/>
+      <c r="Q249" t="inlineStr"/>
+      <c r="R249" t="inlineStr"/>
+      <c r="S249" t="inlineStr"/>
+      <c r="T249" t="inlineStr"/>
+      <c r="U249" t="inlineStr"/>
+      <c r="V249" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -12187,6 +15952,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N250" t="b">
+        <v>0</v>
+      </c>
+      <c r="O250" t="b">
+        <v>0</v>
+      </c>
+      <c r="P250" t="inlineStr"/>
+      <c r="Q250" t="inlineStr"/>
+      <c r="R250" t="inlineStr"/>
+      <c r="S250" t="inlineStr"/>
+      <c r="T250" t="inlineStr"/>
+      <c r="U250" t="inlineStr"/>
+      <c r="V250" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -12234,6 +16014,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N251" t="b">
+        <v>0</v>
+      </c>
+      <c r="O251" t="b">
+        <v>0</v>
+      </c>
+      <c r="P251" t="inlineStr"/>
+      <c r="Q251" t="inlineStr"/>
+      <c r="R251" t="inlineStr"/>
+      <c r="S251" t="inlineStr"/>
+      <c r="T251" t="inlineStr"/>
+      <c r="U251" t="inlineStr"/>
+      <c r="V251" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -12281,6 +16076,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N252" t="b">
+        <v>0</v>
+      </c>
+      <c r="O252" t="b">
+        <v>0</v>
+      </c>
+      <c r="P252" t="inlineStr"/>
+      <c r="Q252" t="inlineStr"/>
+      <c r="R252" t="inlineStr"/>
+      <c r="S252" t="inlineStr"/>
+      <c r="T252" t="inlineStr"/>
+      <c r="U252" t="inlineStr"/>
+      <c r="V252" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -12328,6 +16138,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N253" t="b">
+        <v>0</v>
+      </c>
+      <c r="O253" t="b">
+        <v>0</v>
+      </c>
+      <c r="P253" t="inlineStr"/>
+      <c r="Q253" t="inlineStr"/>
+      <c r="R253" t="inlineStr"/>
+      <c r="S253" t="inlineStr"/>
+      <c r="T253" t="inlineStr"/>
+      <c r="U253" t="inlineStr"/>
+      <c r="V253" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -12375,6 +16200,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N254" t="b">
+        <v>0</v>
+      </c>
+      <c r="O254" t="b">
+        <v>0</v>
+      </c>
+      <c r="P254" t="inlineStr"/>
+      <c r="Q254" t="inlineStr"/>
+      <c r="R254" t="inlineStr"/>
+      <c r="S254" t="inlineStr"/>
+      <c r="T254" t="inlineStr"/>
+      <c r="U254" t="inlineStr"/>
+      <c r="V254" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -12422,6 +16262,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N255" t="b">
+        <v>0</v>
+      </c>
+      <c r="O255" t="b">
+        <v>0</v>
+      </c>
+      <c r="P255" t="inlineStr"/>
+      <c r="Q255" t="inlineStr"/>
+      <c r="R255" t="inlineStr"/>
+      <c r="S255" t="inlineStr"/>
+      <c r="T255" t="inlineStr"/>
+      <c r="U255" t="inlineStr"/>
+      <c r="V255" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -12469,6 +16324,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N256" t="b">
+        <v>0</v>
+      </c>
+      <c r="O256" t="b">
+        <v>0</v>
+      </c>
+      <c r="P256" t="inlineStr"/>
+      <c r="Q256" t="inlineStr"/>
+      <c r="R256" t="inlineStr"/>
+      <c r="S256" t="inlineStr"/>
+      <c r="T256" t="inlineStr"/>
+      <c r="U256" t="inlineStr"/>
+      <c r="V256" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -12516,6 +16386,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N257" t="b">
+        <v>0</v>
+      </c>
+      <c r="O257" t="b">
+        <v>0</v>
+      </c>
+      <c r="P257" t="inlineStr"/>
+      <c r="Q257" t="inlineStr"/>
+      <c r="R257" t="inlineStr"/>
+      <c r="S257" t="inlineStr"/>
+      <c r="T257" t="inlineStr"/>
+      <c r="U257" t="inlineStr"/>
+      <c r="V257" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -12563,6 +16448,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N258" t="b">
+        <v>0</v>
+      </c>
+      <c r="O258" t="b">
+        <v>0</v>
+      </c>
+      <c r="P258" t="inlineStr"/>
+      <c r="Q258" t="inlineStr"/>
+      <c r="R258" t="inlineStr"/>
+      <c r="S258" t="inlineStr"/>
+      <c r="T258" t="inlineStr"/>
+      <c r="U258" t="inlineStr"/>
+      <c r="V258" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -12610,6 +16510,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N259" t="b">
+        <v>0</v>
+      </c>
+      <c r="O259" t="b">
+        <v>0</v>
+      </c>
+      <c r="P259" t="inlineStr"/>
+      <c r="Q259" t="inlineStr"/>
+      <c r="R259" t="inlineStr"/>
+      <c r="S259" t="inlineStr"/>
+      <c r="T259" t="inlineStr"/>
+      <c r="U259" t="inlineStr"/>
+      <c r="V259" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -12657,6 +16572,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N260" t="b">
+        <v>0</v>
+      </c>
+      <c r="O260" t="b">
+        <v>0</v>
+      </c>
+      <c r="P260" t="inlineStr"/>
+      <c r="Q260" t="inlineStr"/>
+      <c r="R260" t="inlineStr"/>
+      <c r="S260" t="inlineStr"/>
+      <c r="T260" t="inlineStr"/>
+      <c r="U260" t="inlineStr"/>
+      <c r="V260" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -12704,6 +16634,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N261" t="b">
+        <v>0</v>
+      </c>
+      <c r="O261" t="b">
+        <v>0</v>
+      </c>
+      <c r="P261" t="inlineStr"/>
+      <c r="Q261" t="inlineStr"/>
+      <c r="R261" t="inlineStr"/>
+      <c r="S261" t="inlineStr"/>
+      <c r="T261" t="inlineStr"/>
+      <c r="U261" t="inlineStr"/>
+      <c r="V261" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -12751,6 +16696,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N262" t="b">
+        <v>0</v>
+      </c>
+      <c r="O262" t="b">
+        <v>0</v>
+      </c>
+      <c r="P262" t="inlineStr"/>
+      <c r="Q262" t="inlineStr"/>
+      <c r="R262" t="inlineStr"/>
+      <c r="S262" t="inlineStr"/>
+      <c r="T262" t="inlineStr"/>
+      <c r="U262" t="inlineStr"/>
+      <c r="V262" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -12798,6 +16758,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N263" t="b">
+        <v>0</v>
+      </c>
+      <c r="O263" t="b">
+        <v>0</v>
+      </c>
+      <c r="P263" t="inlineStr"/>
+      <c r="Q263" t="inlineStr"/>
+      <c r="R263" t="inlineStr"/>
+      <c r="S263" t="inlineStr"/>
+      <c r="T263" t="inlineStr"/>
+      <c r="U263" t="inlineStr"/>
+      <c r="V263" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -12845,6 +16820,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N264" t="b">
+        <v>0</v>
+      </c>
+      <c r="O264" t="b">
+        <v>0</v>
+      </c>
+      <c r="P264" t="inlineStr"/>
+      <c r="Q264" t="inlineStr"/>
+      <c r="R264" t="inlineStr"/>
+      <c r="S264" t="inlineStr"/>
+      <c r="T264" t="inlineStr"/>
+      <c r="U264" t="inlineStr"/>
+      <c r="V264" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -12892,6 +16882,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N265" t="b">
+        <v>0</v>
+      </c>
+      <c r="O265" t="b">
+        <v>0</v>
+      </c>
+      <c r="P265" t="inlineStr"/>
+      <c r="Q265" t="inlineStr"/>
+      <c r="R265" t="inlineStr"/>
+      <c r="S265" t="inlineStr"/>
+      <c r="T265" t="inlineStr"/>
+      <c r="U265" t="inlineStr"/>
+      <c r="V265" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -12939,6 +16944,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N266" t="b">
+        <v>0</v>
+      </c>
+      <c r="O266" t="b">
+        <v>0</v>
+      </c>
+      <c r="P266" t="inlineStr"/>
+      <c r="Q266" t="inlineStr"/>
+      <c r="R266" t="inlineStr"/>
+      <c r="S266" t="inlineStr"/>
+      <c r="T266" t="inlineStr"/>
+      <c r="U266" t="inlineStr"/>
+      <c r="V266" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -12986,6 +17006,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N267" t="b">
+        <v>0</v>
+      </c>
+      <c r="O267" t="b">
+        <v>0</v>
+      </c>
+      <c r="P267" t="inlineStr"/>
+      <c r="Q267" t="inlineStr"/>
+      <c r="R267" t="inlineStr"/>
+      <c r="S267" t="inlineStr"/>
+      <c r="T267" t="inlineStr"/>
+      <c r="U267" t="inlineStr"/>
+      <c r="V267" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -13033,6 +17068,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N268" t="b">
+        <v>0</v>
+      </c>
+      <c r="O268" t="b">
+        <v>0</v>
+      </c>
+      <c r="P268" t="inlineStr"/>
+      <c r="Q268" t="inlineStr"/>
+      <c r="R268" t="inlineStr"/>
+      <c r="S268" t="inlineStr"/>
+      <c r="T268" t="inlineStr"/>
+      <c r="U268" t="inlineStr"/>
+      <c r="V268" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -13080,6 +17130,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N269" t="b">
+        <v>0</v>
+      </c>
+      <c r="O269" t="b">
+        <v>0</v>
+      </c>
+      <c r="P269" t="inlineStr"/>
+      <c r="Q269" t="inlineStr"/>
+      <c r="R269" t="inlineStr"/>
+      <c r="S269" t="inlineStr"/>
+      <c r="T269" t="inlineStr"/>
+      <c r="U269" t="inlineStr"/>
+      <c r="V269" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -13127,6 +17192,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N270" t="b">
+        <v>0</v>
+      </c>
+      <c r="O270" t="b">
+        <v>0</v>
+      </c>
+      <c r="P270" t="inlineStr"/>
+      <c r="Q270" t="inlineStr"/>
+      <c r="R270" t="inlineStr"/>
+      <c r="S270" t="inlineStr"/>
+      <c r="T270" t="inlineStr"/>
+      <c r="U270" t="inlineStr"/>
+      <c r="V270" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -13174,6 +17254,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N271" t="b">
+        <v>0</v>
+      </c>
+      <c r="O271" t="b">
+        <v>0</v>
+      </c>
+      <c r="P271" t="inlineStr"/>
+      <c r="Q271" t="inlineStr"/>
+      <c r="R271" t="inlineStr"/>
+      <c r="S271" t="inlineStr"/>
+      <c r="T271" t="inlineStr"/>
+      <c r="U271" t="inlineStr"/>
+      <c r="V271" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -13221,6 +17316,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N272" t="b">
+        <v>0</v>
+      </c>
+      <c r="O272" t="b">
+        <v>0</v>
+      </c>
+      <c r="P272" t="inlineStr"/>
+      <c r="Q272" t="inlineStr"/>
+      <c r="R272" t="inlineStr"/>
+      <c r="S272" t="inlineStr"/>
+      <c r="T272" t="inlineStr"/>
+      <c r="U272" t="inlineStr"/>
+      <c r="V272" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -13268,6 +17378,21 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N273" t="b">
+        <v>0</v>
+      </c>
+      <c r="O273" t="b">
+        <v>0</v>
+      </c>
+      <c r="P273" t="inlineStr"/>
+      <c r="Q273" t="inlineStr"/>
+      <c r="R273" t="inlineStr"/>
+      <c r="S273" t="inlineStr"/>
+      <c r="T273" t="inlineStr"/>
+      <c r="U273" t="inlineStr"/>
+      <c r="V273" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -13314,6 +17439,21 @@
         <is>
           <t>[]</t>
         </is>
+      </c>
+      <c r="N274" t="b">
+        <v>0</v>
+      </c>
+      <c r="O274" t="b">
+        <v>0</v>
+      </c>
+      <c r="P274" t="inlineStr"/>
+      <c r="Q274" t="inlineStr"/>
+      <c r="R274" t="inlineStr"/>
+      <c r="S274" t="inlineStr"/>
+      <c r="T274" t="inlineStr"/>
+      <c r="U274" t="inlineStr"/>
+      <c r="V274" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
